--- a/Liceo/resultado_3BCH.xlsx
+++ b/Liceo/resultado_3BCH.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,7 +434,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>fila_id</t>
+          <t>carpeta</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -457,6 +457,158 @@
           <t>detalle</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>3BCH-B</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Biología NM IB</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2298</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>TII</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>SUMAINST2</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>FLOOR((SUM(([ID75672]*0.20),([ID75673]*0.20),([ID75674]*0.20),([ID75675]*0.20),([ID75676]*0.20))),0.01)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>3BCH-B</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Biología NM IB</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2298</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TII</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>CALINST2</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>FLOOR(([ID90299]*0.70),0.01)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3BCH-B</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Biología NM IB</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2298</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TII</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CALEXAT2</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>FLOOR(([ID75678]*0.30),0.01)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3BCH-B</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Biología NM IB</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2298</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TII</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>PROMTRI2</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>FLOOR(([ID75692]+[ID75677]),0.01)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
